--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5065,6 +5065,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>缇外 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>院墅A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>院墅B</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>院墅C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>院墅A
+10692呎 (4+房)
+(24年-08月-28日)
+$10.28亿
+$96,147/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>院墅B
+11589呎 (4+房)
+(24年-04月-24日)
+$10.00亿
+$86,289/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>院墅C
+11145呎 (4+房)
+(25年-05月-27日)
+$10.00亿
+$89,726/呎</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5308,284 +5459,6 @@
       <c r="C10" s="20" t="inlineStr"/>
       <c r="D10" s="20" t="inlineStr"/>
       <c r="E10" s="20" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>PH | 8495呎 (4+房)
-$63600万
-$74,868/呎
-(24年-02月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 4451呎 (4+房)
-$25816万
-$58,000/呎
-(22年-11月-16日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$23500万
-$55,190/呎
-(24年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$26000万
-$59,158/呎
-(24年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 4364呎 (4+房)
-$24002万
-$55,000/呎
-(23年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$22500万
-$51,195/呎
-(24年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$22500万
-$52,842/呎
-(24年-11月-15日)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 4395呎 (4+房)
-$19000万
-$43,231/呎
-(26年-02月-04日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 4258呎 (4+房)
-$19500万
-$45,796/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 4236呎 (4+房)
-$17680万
-$41,737/呎
-(26年-01月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 4099呎 (4+房)
-$18500万
-$45,133/呎
-(25年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 4431呎 (4+房)
-$20850万
-$47,055/呎
-(24年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 3955呎 (4+房)
-$17100万
-$43,236/呎
-(24年-11月-04日)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5614,7 +5487,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5541,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5678,7 +5551,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5714,10 +5587,10 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8402呎 (4+房)
-$60000万
-$71,412/呎
-(25年-10月-13日)</t>
+          <t>PH | 8495呎 (4+房)
+$63600万
+$74,868/呎
+(24年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -5729,18 +5602,18 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
-$25000万
-$57,104/呎
-(24年-07月-02日)</t>
+          <t>A | 4451呎 (4+房)
+$25816万
+$58,000/呎
+(22年-11月-16日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
-$25000万
-$56,896/呎
-(24年-07月-19日)</t>
+          <t>B | 4258呎 (4+房)
+$23500万
+$55,190/呎
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5753,18 +5626,18 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
-$25580万
-$58,429/呎
-(24年-06月-28日)</t>
+          <t>A | 4395呎 (4+房)
+$26000万
+$59,158/呎
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4557呎 (4+房)
-$24500万
-$53,763/呎
-(23年-12月-22日)</t>
+          <t>B | 4364呎 (4+房)
+$24002万
+$55,000/呎
+(23年-08月-29日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5777,18 +5650,18 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
-$23000万
-$52,535/呎
-(24年-08月-08日)</t>
+          <t>A | 4395呎 (4+房)
+$22500万
+$51,195/呎
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
-$22000万
-$50,068/呎
-(24年-09月-16日)</t>
+          <t>B | 4258呎 (4+房)
+$22500万
+$52,842/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5801,18 +5674,18 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4378呎 (4+房)
-$19200万
-$43,856/呎
-(25年-12月-17日)</t>
+          <t>A | 4395呎 (4+房)
+$19000万
+$43,231/呎
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 4394呎 (4+房)
-$19200万
-$43,696/呎
-(24年-12月-06日)</t>
+          <t>B | 4258呎 (4+房)
+$19500万
+$45,796/呎
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5823,20 +5696,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>A | 4324呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 4398呎 (4+房)
--
--
-(待售)</t>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4236呎 (4+房)
+$17680万
+$41,737/呎
+(26年-01月-29日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 4099呎 (4+房)
+$18500万
+$45,133/呎
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -5849,18 +5722,18 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4072呎 (4+房)
-$18000万
-$44,204/呎
-(24年-08月-06日)</t>
+          <t>A | 4431呎 (4+房)
+$20850万
+$47,055/呎
+(24年-01月-19日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 4311呎 (4+房)
-$20850万
-$48,365/呎
-(24年-09月-30日)</t>
+          <t>B | 3955呎 (4+房)
+$17100万
+$43,236/呎
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -5892,7 +5765,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>5座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5819,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5956,7 +5829,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -5992,10 +5865,10 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8283呎 (4+房)
-$58000万
-$70,023/呎
-(25年-11月-06日)</t>
+          <t>PH | 8402呎 (4+房)
+$60000万
+$71,412/呎
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -6005,118 +5878,118 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 4332呎 (4+房)
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(24年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$25000万
+$56,896/呎
+(24年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$25580万
+$58,429/呎
+(24年-06月-28日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4557呎 (4+房)
+$24500万
+$53,763/呎
+(23年-12月-22日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(24年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$22000万
+$50,068/呎
+(24年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4378呎 (4+房)
+$19200万
+$43,856/呎
+(25年-12月-17日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 4394呎 (4+房)
+$19200万
+$43,696/呎
+(24年-12月-06日)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 4324呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$25000万
-$57,104/呎
-(25年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 4437呎 (4+房)
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4398呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$23000万
-$53,814/呎
-(25年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$23000万
-$52,535/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$19180万
-$44,876/呎
-(24年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 4116呎 (4+房)
-$18500万
-$44,947/呎
-(25年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 4325呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
@@ -6127,18 +6000,18 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4194呎 (4+房)
-$18500万
-$44,111/呎
-(24年-10月-21日)</t>
+          <t>A | 4072呎 (4+房)
+$18000万
+$44,204/呎
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>B | 4074呎 (4+房)
-$18000万
-$44,183/呎
-(24年-07月-23日)</t>
+          <t>B | 4311呎 (4+房)
+$20850万
+$48,365/呎
+(24年-09月-30日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6153,6 +6026,284 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH | 8283呎 (4+房)
+$58000万
+$70,023/呎
+(25年-11月-06日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 4332呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(25年-12月-05日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 4437呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$23000万
+$53,814/呎
+(25年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$19180万
+$44,876/呎
+(24年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4116呎 (4+房)
+$18500万
+$44,947/呎
+(25年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4325呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 4194呎 (4+房)
+$18500万
+$44,111/呎
+(24年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 4074呎 (4+房)
+$18000万
+$44,183/呎
+(24年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6423,155 +6574,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 独立屋销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>院墅A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>院墅B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>院墅C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>院墅A
-10692呎 (4+房)
-(24年-08月-28日)
-$10.28亿
-$96,147/呎</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>院墅B
-11589呎 (4+房)
-(24年-04月-24日)
-$10.00亿
-$86,289/呎</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>院墅C
-11145呎 (4+房)
-(25年-05月-27日)
-$10.00亿
-$89,726/呎</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5065,24 +5065,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>缇外 - 独立屋销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -5113,97 +5114,204 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>类型/位置</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>院墅A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>院墅B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>院墅C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>独立屋</t>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>PH A</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>PH B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6&amp;7</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>PH A | 7912呎 (4+房)
+$60000万
+$75,834/呎
+(24年-05月-09日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>PH B | 8583呎 (4+房)
+$61900万
+$72,119/呎
+(24年-02月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>院墅A
-10692呎 (4+房)
-(24年-08月-28日)
-$10.28亿
-$96,147/呎</t>
+          <t>A | 4247呎 (4+房)
+$22750万
+$53,567/呎
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>院墅B
-11589呎 (4+房)
-(24年-04月-24日)
-$10.00亿
-$86,289/呎</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>院墅C
-11145呎 (4+房)
-(25年-05月-27日)
-$10.00亿
-$89,726/呎</t>
-        </is>
-      </c>
+          <t>B | 4374呎 (4+房)
+$24057万
+$55,000/呎
+(22年-11月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 4247呎 (4+房)
+$21600万
+$50,859/呎
+(24年-06月-20日)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 4436呎 (4+房)
+$24000万
+$54,103/呎
+(24年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4359呎 (4+房)
+$20000万
+$45,882/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4335呎 (4+房)
+$21500万
+$49,596/呎
+(26年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4269呎 (4+房)
+$21000万
+$49,192/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4071呎 (4+房)
+$17200万
+$42,250/呎
+(25年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5216,20 +5324,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>1座 销控网格图</t>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5375,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -5283,7 +5390,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5315,150 +5422,170 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>PH A</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>PH B</t>
+          <t>PH</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>6&amp;7</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH A | 7912呎 (4+房)
-$60000万
-$75,834/呎
-(24年-05月-09日)</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>PH B | 8583呎 (4+房)
-$61900万
-$72,119/呎
-(24年-02月-09日)</t>
+          <t>PH | 8495呎 (4+房)
+$63600万
+$74,868/呎
+(24年-02月-22日)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 4247呎 (4+房)
-$22750万
-$53,567/呎
-(25年-04月-30日)</t>
+          <t>A | 4451呎 (4+房)
+$25816万
+$58,000/呎
+(22年-11月-16日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 4374呎 (4+房)
-$24057万
-$55,000/呎
-(22年-11月-01日)</t>
+          <t>B | 4258呎 (4+房)
+$23500万
+$55,190/呎
+(24年-03月-12日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4247呎 (4+房)
-$21600万
-$50,859/呎
-(24年-06月-20日)</t>
+          <t>A | 4395呎 (4+房)
+$26000万
+$59,158/呎
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4436呎 (4+房)
-$24000万
-$54,103/呎
-(24年-01月-12日)</t>
+          <t>B | 4364呎 (4+房)
+$24002万
+$55,000/呎
+(23年-08月-29日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4359呎 (4+房)
-$20000万
-$45,882/呎
-(26年-07月-24日)</t>
+          <t>A | 4395呎 (4+房)
+$22500万
+$51,195/呎
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4335呎 (4+房)
-$21500万
-$49,596/呎
-(26年-07月-23日)</t>
+          <t>B | 4258呎 (4+房)
+$22500万
+$52,842/呎
+(24年-11月-15日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
-      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4269呎 (4+房)
-$21000万
-$49,192/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr"/>
+          <t>A | 4395呎 (4+房)
+$19000万
+$43,231/呎
+(26年-02月-04日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 4258呎 (4+房)
+$19500万
+$45,796/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
       <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4236呎 (4+房)
+$17680万
+$41,737/呎
+(26年-01月-29日)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 4099呎 (4+房)
+$18500万
+$45,133/呎
+(25年-12月-22日)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 4071呎 (4+房)
-$17200万
-$42,250/呎
-(25年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="20" t="inlineStr"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 4431呎 (4+房)
+$20850万
+$47,055/呎
+(24年-01月-19日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 3955呎 (4+房)
+$17100万
+$43,236/呎
+(24年-11月-04日)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5487,7 +5614,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>2座 销控网格图</t>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5668,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5551,7 +5678,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -5587,10 +5714,10 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8495呎 (4+房)
-$63600万
-$74,868/呎
-(24年-02月-22日)</t>
+          <t>PH | 8402呎 (4+房)
+$60000万
+$71,412/呎
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -5602,18 +5729,18 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 4451呎 (4+房)
-$25816万
-$58,000/呎
-(22年-11月-16日)</t>
+          <t>A | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>B | 4258呎 (4+房)
-$23500万
-$55,190/呎
-(24年-03月-12日)</t>
+          <t>B | 4394呎 (4+房)
+$25000万
+$56,896/呎
+(24年-07月-19日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>
@@ -5626,18 +5753,18 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
-$26000万
-$59,158/呎
-(24年-10月-07日)</t>
+          <t>A | 4378呎 (4+房)
+$25580万
+$58,429/呎
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 4364呎 (4+房)
-$24002万
-$55,000/呎
-(23年-08月-29日)</t>
+          <t>B | 4557呎 (4+房)
+$24500万
+$53,763/呎
+(23年-12月-22日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr"/>
@@ -5650,18 +5777,18 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
-$22500万
-$51,195/呎
-(24年-04月-16日)</t>
+          <t>A | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(24年-08月-08日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 4258呎 (4+房)
-$22500万
-$52,842/呎
-(24年-11月-15日)</t>
+          <t>B | 4394呎 (4+房)
+$22000万
+$50,068/呎
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr"/>
@@ -5674,18 +5801,18 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 4395呎 (4+房)
-$19000万
-$43,231/呎
-(26年-02月-04日)</t>
+          <t>A | 4378呎 (4+房)
+$19200万
+$43,856/呎
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>B | 4258呎 (4+房)
-$19500万
-$45,796/呎
-(26年-02月-27日)</t>
+          <t>B | 4394呎 (4+房)
+$19200万
+$43,696/呎
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -5696,20 +5823,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 4236呎 (4+房)
-$17680万
-$41,737/呎
-(26年-01月-29日)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 4099呎 (4+房)
-$18500万
-$45,133/呎
-(25年-12月-22日)</t>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 4324呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4398呎 (4+房)
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -5722,18 +5849,18 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4431呎 (4+房)
+          <t>A | 4072呎 (4+房)
+$18000万
+$44,204/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 4311呎 (4+房)
 $20850万
-$47,055/呎
-(24年-01月-19日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 3955呎 (4+房)
-$17100万
-$43,236/呎
-(24年-11月-04日)</t>
+$48,365/呎
+(24年-09月-30日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -5765,7 +5892,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>3座 销控网格图</t>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5946,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5829,7 +5956,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5865,10 +5992,10 @@
       <c r="C5" s="20" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>PH | 8402呎 (4+房)
-$60000万
-$71,412/呎
-(25年-10月-13日)</t>
+          <t>PH | 8283呎 (4+房)
+$58000万
+$70,023/呎
+(25年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -5878,118 +6005,118 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$25000万
-$57,104/呎
-(24年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$25000万
-$56,896/呎
-(24年-07月-19日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$25580万
-$58,429/呎
-(24年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 4557呎 (4+房)
-$24500万
-$53,763/呎
-(23年-12月-22日)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$23000万
-$52,535/呎
-(24年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$22000万
-$50,068/呎
-(24年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 4378呎 (4+房)
-$19200万
-$43,856/呎
-(25年-12月-17日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 4394呎 (4+房)
-$19200万
-$43,696/呎
-(24年-12月-06日)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>A | 4324呎 (4+房)
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 4332呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 4398呎 (4+房)
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$25000万
+$57,104/呎
+(25年-12月-05日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 4437呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$23000万
+$53,814/呎
+(25年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 4378呎 (4+房)
+$23000万
+$52,535/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 4274呎 (4+房)
+$19180万
+$44,876/呎
+(24年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 4483呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 4116呎 (4+房)
+$18500万
+$44,947/呎
+(25年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 4325呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
@@ -6000,18 +6127,18 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 4072呎 (4+房)
+          <t>A | 4194呎 (4+房)
+$18500万
+$44,111/呎
+(24年-10月-21日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 4074呎 (4+房)
 $18000万
-$44,204/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 4311呎 (4+房)
-$20850万
-$48,365/呎
-(24年-09月-30日)</t>
+$44,183/呎
+(24年-07月-23日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -6026,284 +6153,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>PH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>PH | 8283呎 (4+房)
-$58000万
-$70,023/呎
-(25年-11月-06日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>A | 4332呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$25000万
-$57,104/呎
-(25年-12月-05日)</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>A | 4437呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr"/>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$23000万
-$53,814/呎
-(25年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 4378呎 (4+房)
-$23000万
-$52,535/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr"/>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 4274呎 (4+房)
-$19180万
-$44,876/呎
-(24年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 4483呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 4116呎 (4+房)
-$18500万
-$44,947/呎
-(25年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 4325呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 4194呎 (4+房)
-$18500万
-$44,111/呎
-(24年-10月-21日)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 4074呎 (4+房)
-$18000万
-$44,183/呎
-(24年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6574,4 +6423,155 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>缇外 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>3 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>院墅A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>院墅B</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>院墅C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>院墅A
+10692呎 (4+房)
+(24年-08月-28日)
+$10.28亿
+$96,147/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>院墅B
+11589呎 (4+房)
+(24年-04月-24日)
+$10.00亿
+$86,289/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>院墅C
+11145呎 (4+房)
+(25年-05月-27日)
+$10.00亿
+$89,726/呎</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4359</v>
+        <v>4247</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
         <v>200000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>45882</v>
+        <v>47092</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 4359呎 (4+房)
+          <t>A | 4247呎 (4+房)
 $20000万
-$45,882/呎
-(26年-07月-24日)</t>
+$47,092/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -236,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -304,19 +310,22 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4140,7 +4149,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4150,12 +4159,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4165,12 +4174,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4180,7 +4189,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6215,27 +6224,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6283,12 @@
       </c>
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>PH A | 7403呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -6480,32 +6489,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4149,23 +4149,19 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>580000000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>78347</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4174,12 +4170,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4189,7 +4185,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5945,27 +5941,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6118,12 +6114,12 @@
 (25年-02月-24日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 4325呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -6224,7 +6220,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6234,7 +6230,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6283,12 +6279,12 @@
       </c>
       <c r="B5" s="20" t="inlineStr"/>
       <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>PH A | 7403呎 (4+房)
-招标单位
--
-(在售)</t>
+$58000万
+$78,347/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">

--- a/web/files/九龙-九龙塘-缇外.xlsx
+++ b/web/files/九龙-九龙塘-缇外.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,12 +127,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -242,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -310,22 +304,19 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3811,23 +3802,19 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>46243</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3836,12 +3823,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3851,7 +3838,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5928,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5951,7 +5938,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6114,12 +6101,12 @@
 (25年-02月-24日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 4325呎 (4+房)
-招标单位
--
-(在售)</t>
+$20000万
+$46,243/呎
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -6485,32 +6472,32 @@
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>3 套</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
